--- a/tests/Data/REEXPAllState.xlsx
+++ b/tests/Data/REEXPAllState.xlsx
@@ -351,7 +351,7 @@
     <t xml:space="preserve">NorthStar Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123  michigan mi usa</t>
+    <t xml:space="preserve">michigan mi usa</t>
   </si>
   <si>
     <t xml:space="preserve">20</t>
@@ -567,7 +567,7 @@
     <t xml:space="preserve">Rushmore Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 South Carolina SC usa</t>
+    <t xml:space="preserve">South Carolina SC usa</t>
   </si>
   <si>
     <t xml:space="preserve">36</t>
@@ -621,7 +621,7 @@
     <t xml:space="preserve">Maple Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Virginia VA usa</t>
+    <t xml:space="preserve">Virginia VA usa</t>
   </si>
   <si>
     <t xml:space="preserve">41</t>
@@ -1015,48 +1015,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1312,1990 +1316,1990 @@
   <dimension ref="A1:U37"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="4.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="25.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="3.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="25.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5" t="s">
+      <c r="F2" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="S2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="B3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5" t="s">
+      <c r="F3" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="S3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5" t="s">
+      <c r="F4" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" s="5" t="s">
+      <c r="S4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5" t="s">
+      <c r="F5" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="S5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="U5" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5" t="s">
+      <c r="F6" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q6" s="5" t="s">
+      <c r="Q6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="R6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="5" t="s">
+      <c r="S6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5" t="s">
+      <c r="F7" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="Q7" s="5" t="s">
+      <c r="Q7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="5" t="s">
+      <c r="R7" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="S7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="5" t="s">
+      <c r="S7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U7" s="8" t="s">
+      <c r="U7" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5" t="s">
+      <c r="F8" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="Q8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="R8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="5" t="s">
+      <c r="S8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="U8" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5" t="s">
+      <c r="F9" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="Q9" s="5" t="s">
+      <c r="Q9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="R9" s="5" t="s">
+      <c r="R9" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="S9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="5" t="s">
+      <c r="S9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U9" s="8" t="s">
+      <c r="U9" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="B10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5" t="s">
+      <c r="F10" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="Q10" s="5" t="s">
+      <c r="Q10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R10" s="5" t="s">
+      <c r="R10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T10" s="5" t="s">
+      <c r="S10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U10" s="8" t="s">
+      <c r="U10" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="B11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5" t="s">
+      <c r="F11" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="Q11" s="5" t="s">
+      <c r="Q11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="R11" s="5" t="s">
+      <c r="R11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="S11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" s="5" t="s">
+      <c r="S11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U11" s="8" t="s">
+      <c r="U11" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="B12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="F12" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5" t="s">
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="Q12" s="5" t="s">
+      <c r="Q12" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="R12" s="5" t="s">
+      <c r="R12" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="S12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T12" s="5" t="s">
+      <c r="S12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U12" s="8" t="s">
+      <c r="U12" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5" t="s">
+      <c r="F13" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="Q13" s="5" t="s">
+      <c r="Q13" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="R13" s="5" t="s">
+      <c r="R13" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="S13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T13" s="5" t="s">
+      <c r="S13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U13" s="8" t="s">
+      <c r="U13" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="B14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5" t="s">
+      <c r="F14" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q14" s="5" t="s">
+      <c r="Q14" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R14" s="5" t="s">
+      <c r="R14" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="S14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T14" s="5" t="s">
+      <c r="S14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U14" s="8" t="s">
+      <c r="U14" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="B15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5" t="s">
+      <c r="F15" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="Q15" s="5" t="s">
+      <c r="Q15" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="R15" s="5" t="s">
+      <c r="R15" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="S15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" s="5" t="s">
+      <c r="S15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U15" s="8" t="s">
+      <c r="U15" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="B16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5" t="s">
+      <c r="F16" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q16" s="5" t="s">
+      <c r="Q16" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="R16" s="5" t="s">
+      <c r="R16" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="S16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T16" s="5" t="s">
+      <c r="S16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U16" s="8" t="s">
+      <c r="U16" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="B17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5" t="s">
+      <c r="F17" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Q17" s="5" t="s">
+      <c r="Q17" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="R17" s="5" t="s">
+      <c r="R17" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="S17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T17" s="5" t="s">
+      <c r="S17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U17" s="8" t="s">
+      <c r="U17" s="9" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="9" t="s">
+      <c r="B18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5" t="s">
+      <c r="F18" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="Q18" s="5" t="s">
+      <c r="Q18" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="R18" s="5" t="s">
+      <c r="R18" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="S18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T18" s="5" t="s">
+      <c r="S18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U18" s="8" t="s">
+      <c r="U18" s="9" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="9" t="s">
+      <c r="B19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F19" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5" t="s">
+      <c r="F19" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="Q19" s="5" t="s">
+      <c r="Q19" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="R19" s="5" t="s">
+      <c r="R19" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="S19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T19" s="5" t="s">
+      <c r="S19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U19" s="8" t="s">
+      <c r="U19" s="9" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="B20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5" t="s">
+      <c r="F20" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="Q20" s="5" t="s">
+      <c r="Q20" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="R20" s="5" t="s">
+      <c r="R20" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="S20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T20" s="5" t="s">
+      <c r="S20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U20" s="8" t="s">
+      <c r="U20" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="B21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F21" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5" t="s">
+      <c r="F21" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="Q21" s="5" t="s">
+      <c r="Q21" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="R21" s="5" t="s">
+      <c r="R21" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="S21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T21" s="5" t="s">
+      <c r="S21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U21" s="8" t="s">
+      <c r="U21" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="B22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5" t="s">
+      <c r="F22" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="Q22" s="5" t="s">
+      <c r="Q22" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="R22" s="5" t="s">
+      <c r="R22" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="S22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T22" s="5" t="s">
+      <c r="S22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U22" s="8" t="s">
+      <c r="U22" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="B23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5" t="s">
+      <c r="F23" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="Q23" s="5" t="s">
+      <c r="Q23" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="R23" s="5" t="s">
+      <c r="R23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="S23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T23" s="5" t="s">
+      <c r="S23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="U23" s="9" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="9" t="s">
+      <c r="B24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5" t="s">
+      <c r="F24" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="Q24" s="5" t="s">
+      <c r="Q24" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="R24" s="5" t="s">
+      <c r="R24" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="S24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T24" s="5" t="s">
+      <c r="S24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T24" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U24" s="8" t="s">
+      <c r="U24" s="9" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="B25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5" t="s">
+      <c r="F25" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="Q25" s="5" t="s">
+      <c r="Q25" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="R25" s="5" t="s">
+      <c r="R25" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="S25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T25" s="5" t="s">
+      <c r="S25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U25" s="8" t="s">
+      <c r="U25" s="9" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="9" t="s">
+      <c r="B26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5" t="s">
+      <c r="F26" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="Q26" s="5" t="s">
+      <c r="Q26" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="R26" s="5" t="s">
+      <c r="R26" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="S26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T26" s="5" t="s">
+      <c r="S26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U26" s="8" t="s">
+      <c r="U26" s="9" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="9" t="s">
+      <c r="B27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5" t="s">
+      <c r="F27" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="Q27" s="5" t="s">
+      <c r="Q27" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="R27" s="5" t="s">
+      <c r="R27" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="S27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T27" s="5" t="s">
+      <c r="S27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T27" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U27" s="8" t="s">
+      <c r="U27" s="9" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="9" t="s">
+      <c r="B28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5" t="s">
+      <c r="F28" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="Q28" s="5" t="s">
+      <c r="Q28" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="R28" s="5" t="s">
+      <c r="R28" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="S28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T28" s="5" t="s">
+      <c r="S28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T28" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U28" s="8" t="s">
+      <c r="U28" s="9" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="B29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5" t="s">
+      <c r="F29" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="Q29" s="5" t="s">
+      <c r="Q29" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="R29" s="5" t="s">
+      <c r="R29" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="S29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T29" s="5" t="s">
+      <c r="S29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U29" s="8" t="s">
+      <c r="U29" s="9" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="9" t="s">
+      <c r="B30" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5" t="s">
+      <c r="F30" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="Q30" s="5" t="s">
+      <c r="Q30" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="R30" s="5" t="s">
+      <c r="R30" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="S30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T30" s="5" t="s">
+      <c r="S30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T30" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U30" s="8" t="s">
+      <c r="U30" s="9" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="9" t="s">
+      <c r="B31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5" t="s">
+      <c r="F31" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="Q31" s="5" t="s">
+      <c r="Q31" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="R31" s="5" t="s">
+      <c r="R31" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="S31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T31" s="5" t="s">
+      <c r="S31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U31" s="8" t="s">
+      <c r="U31" s="9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="9" t="s">
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5" t="s">
+      <c r="F32" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="Q32" s="5" t="s">
+      <c r="Q32" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="R32" s="5" t="s">
+      <c r="R32" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="S32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T32" s="5" t="s">
+      <c r="S32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U32" s="8" t="s">
+      <c r="U32" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="B33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5" t="s">
+      <c r="F33" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="Q33" s="5" t="s">
+      <c r="Q33" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="R33" s="5" t="s">
+      <c r="R33" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="S33" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T33" s="5" t="s">
+      <c r="S33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T33" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U33" s="8" t="s">
+      <c r="U33" s="9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="9" t="s">
+      <c r="F34" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="Q34" s="5" t="s">
+      <c r="Q34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="R34" s="5" t="s">
+      <c r="R34" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="S34" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T34" s="5" t="s">
+      <c r="S34" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T34" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U34" s="8" t="s">
+      <c r="U34" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F35" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="9" t="s">
+      <c r="F35" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="Q35" s="5" t="s">
+      <c r="Q35" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="R35" s="5" t="s">
+      <c r="R35" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="S35" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T35" s="5" t="s">
+      <c r="S35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U35" s="8" t="s">
+      <c r="U35" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F36" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5" t="s">
+      <c r="F36" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="Q36" s="5" t="s">
+      <c r="Q36" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R36" s="5" t="s">
+      <c r="R36" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="S36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T36" s="5" t="s">
+      <c r="S36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T36" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U36" s="8" t="s">
+      <c r="U36" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F37" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5" t="s">
+      <c r="F37" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="Q37" s="5" t="s">
+      <c r="Q37" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="R37" s="5" t="s">
+      <c r="R37" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="S37" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T37" s="5" t="s">
+      <c r="S37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T37" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U37" s="8" t="s">
+      <c r="U37" s="9" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3318,144 +3322,144 @@
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="4.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="25.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="20.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="6.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="25.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="17.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="20.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="6.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5" t="s">
+      <c r="F2" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="S2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3479,532 +3483,532 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5" t="s">
+      <c r="F1" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="5" t="n">
+      <c r="Q1" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="R1" s="5" t="n">
+      <c r="R1" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="S1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="5" t="n">
+      <c r="S1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5" t="s">
+      <c r="F2" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="S2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="9" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="B3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5" t="s">
+      <c r="F3" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="S3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="9" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5" t="s">
+      <c r="F4" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="S4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" s="5" t="s">
+      <c r="S4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="9" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5" t="s">
+      <c r="F5" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q5" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="S5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="U5" s="9" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5" t="s">
+      <c r="F6" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="Q6" s="5" t="s">
+      <c r="Q6" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="R6" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="5" t="s">
+      <c r="S6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="9" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5" t="s">
+      <c r="F7" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="Q7" s="5" t="s">
+      <c r="Q7" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="R7" s="5" t="s">
+      <c r="R7" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="S7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="5" t="s">
+      <c r="S7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U7" s="8" t="s">
+      <c r="U7" s="9" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5" t="s">
+      <c r="F8" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="Q8" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="R8" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="5" t="s">
+      <c r="S8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="U8" s="9" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5" t="s">
+      <c r="F9" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="Q9" s="5" t="s">
+      <c r="Q9" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="R9" s="5" t="s">
+      <c r="R9" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="S9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="5" t="s">
+      <c r="S9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U9" s="8" t="s">
+      <c r="U9" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="B10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5" t="s">
+      <c r="F10" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Q10" s="5" t="s">
+      <c r="Q10" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="R10" s="5" t="s">
+      <c r="R10" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="S10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T10" s="5" t="s">
+      <c r="S10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U10" s="8" t="s">
+      <c r="U10" s="9" t="s">
         <v>287</v>
       </c>
     </row>

--- a/tests/Data/REEXPAllState.xlsx
+++ b/tests/Data/REEXPAllState.xlsx
@@ -603,7 +603,7 @@
     <t xml:space="preserve">Virginia Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Utah UT usa</t>
+    <t xml:space="preserve">meridian Utah UT USA</t>
   </si>
   <si>
     <t xml:space="preserve">40</t>
@@ -621,7 +621,7 @@
     <t xml:space="preserve">Maple Test</t>
   </si>
   <si>
-    <t xml:space="preserve">Virginia VA usa</t>
+    <t xml:space="preserve">123 Virginia Avenue  VA USA</t>
   </si>
   <si>
     <t xml:space="preserve">41</t>
@@ -1317,9 +1317,11 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="3.67"/>

--- a/tests/Data/REEXPAllState.xlsx
+++ b/tests/Data/REEXPAllState.xlsx
@@ -147,7 +147,7 @@
     <t xml:space="preserve">File Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Arkansas AR usa</t>
+    <t xml:space="preserve">123 South Arkansas AR usa</t>
   </si>
   <si>
     <t xml:space="preserve">7</t>
@@ -351,7 +351,7 @@
     <t xml:space="preserve">NorthStar Test</t>
   </si>
   <si>
-    <t xml:space="preserve">michigan mi usa</t>
+    <t xml:space="preserve">South michigan mi usa</t>
   </si>
   <si>
     <t xml:space="preserve">20</t>
@@ -621,7 +621,7 @@
     <t xml:space="preserve">Maple Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Virginia Avenue  VA USA</t>
+    <t xml:space="preserve">Virginia Avenue  VA USA</t>
   </si>
   <si>
     <t xml:space="preserve">41</t>
@@ -1319,8 +1319,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.33"/>

--- a/tests/Data/REEXPAllState.xlsx
+++ b/tests/Data/REEXPAllState.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="285">
   <si>
     <t xml:space="preserve">State</t>
   </si>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">HHL01-A, Herbert H. Landy</t>
   </si>
   <si>
-    <t xml:space="preserve">Lake Test</t>
+    <t xml:space="preserve">COLONIAL SURETY COMPANY</t>
   </si>
   <si>
     <t xml:space="preserve">Unlimited</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">AZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Work Test</t>
+    <t xml:space="preserve">CUMIS INSURANCE SOCIETY, INC.</t>
   </si>
   <si>
     <t xml:space="preserve">123 Arizona AZ usa</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
-    <t xml:space="preserve">File Test</t>
+    <t xml:space="preserve">SureTec Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 South Arkansas AR usa</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">CT</t>
   </si>
   <si>
-    <t xml:space="preserve">Document Test</t>
+    <t xml:space="preserve">Seneca Insurance Company, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">123 Connecticut CT usa ct</t>
@@ -180,10 +180,10 @@
     <t xml:space="preserve">DE</t>
   </si>
   <si>
-    <t xml:space="preserve">Formula Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Delaware DE usa</t>
+    <t xml:space="preserve">First Net Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delaware DE usa</t>
   </si>
   <si>
     <t xml:space="preserve">9</t>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">GA</t>
   </si>
   <si>
-    <t xml:space="preserve">Island Test</t>
+    <t xml:space="preserve">Brierfield Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Georgia GA usa</t>
@@ -216,7 +216,7 @@
     <t xml:space="preserve">HI</t>
   </si>
   <si>
-    <t xml:space="preserve">Corn Test</t>
+    <t xml:space="preserve">Amerisure Partners Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">hawai hi usa</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">IL</t>
   </si>
   <si>
-    <t xml:space="preserve">Hoosier Test</t>
+    <t xml:space="preserve">Arch Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Illinois IL usa</t>
@@ -255,10 +255,10 @@
     <t xml:space="preserve">IN</t>
   </si>
   <si>
-    <t xml:space="preserve">Sunflower Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Indiana IN usa</t>
+    <t xml:space="preserve">Endurance Assurance Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indiana IN usa</t>
   </si>
   <si>
     <t xml:space="preserve">15</t>
@@ -273,7 +273,7 @@
     <t xml:space="preserve">KS</t>
   </si>
   <si>
-    <t xml:space="preserve">Bluegrass Test</t>
+    <t xml:space="preserve">International Fidelity Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Kansas KS usa</t>
@@ -291,7 +291,7 @@
     <t xml:space="preserve">MA</t>
   </si>
   <si>
-    <t xml:space="preserve">Chesapeake Test</t>
+    <t xml:space="preserve">Merchants National Bonding, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">s</t>
@@ -312,7 +312,7 @@
     <t xml:space="preserve">MD</t>
   </si>
   <si>
-    <t xml:space="preserve">Pine Test</t>
+    <t xml:space="preserve">GENERAL STAR NATIONAL INSURANCE COMPANY</t>
   </si>
   <si>
     <t xml:space="preserve">123 Maryland MD usa</t>
@@ -330,7 +330,7 @@
     <t xml:space="preserve">ME</t>
   </si>
   <si>
-    <t xml:space="preserve">GreatLake Test</t>
+    <t xml:space="preserve">General Star National Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">Maine ME usa</t>
@@ -348,7 +348,7 @@
     <t xml:space="preserve">MI</t>
   </si>
   <si>
-    <t xml:space="preserve">NorthStar Test</t>
+    <t xml:space="preserve">National Casualty Company</t>
   </si>
   <si>
     <t xml:space="preserve">South michigan mi usa</t>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">MN</t>
   </si>
   <si>
-    <t xml:space="preserve">ShowMe Test</t>
+    <t xml:space="preserve">First Founders Assurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Minnesota MN usa</t>
@@ -384,9 +384,6 @@
     <t xml:space="preserve">MO</t>
   </si>
   <si>
-    <t xml:space="preserve">Magnolia Test</t>
-  </si>
-  <si>
     <t xml:space="preserve">123 Missouri MO usa</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
     <t xml:space="preserve">MT</t>
   </si>
   <si>
-    <t xml:space="preserve">TarHeel Test</t>
-  </si>
-  <si>
     <t xml:space="preserve">123 Montana MT usa MT</t>
   </si>
   <si>
@@ -420,9 +414,6 @@
     <t xml:space="preserve">NH</t>
   </si>
   <si>
-    <t xml:space="preserve">Garden Test</t>
-  </si>
-  <si>
     <t xml:space="preserve">123 New Hampshire NH usa</t>
   </si>
   <si>
@@ -438,7 +429,7 @@
     <t xml:space="preserve">NV</t>
   </si>
   <si>
-    <t xml:space="preserve">Empire Test</t>
+    <t xml:space="preserve">Pennsylvania Manufacturers' Association Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">Neveda Mediacl Nv USa</t>
@@ -456,7 +447,7 @@
     <t xml:space="preserve">NY</t>
   </si>
   <si>
-    <t xml:space="preserve">Buckeye Test</t>
+    <t xml:space="preserve">SOUTHWEST MARINE AND GENERAL INSURANCE COMPANY</t>
   </si>
   <si>
     <t xml:space="preserve">New York NY usa</t>
@@ -474,7 +465,7 @@
     <t xml:space="preserve">OH</t>
   </si>
   <si>
-    <t xml:space="preserve">Sooner Test</t>
+    <t xml:space="preserve">Protective Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Ohio OH usa</t>
@@ -492,7 +483,7 @@
     <t xml:space="preserve">OK</t>
   </si>
   <si>
-    <t xml:space="preserve">Beaver Test</t>
+    <t xml:space="preserve">Selective Insurance Company of America</t>
   </si>
   <si>
     <t xml:space="preserve">123 Oklahoma OK usa</t>
@@ -510,7 +501,7 @@
     <t xml:space="preserve">OR</t>
   </si>
   <si>
-    <t xml:space="preserve">Keystone Test</t>
+    <t xml:space="preserve">Developers Surety and Indemnity Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Oregon OR usa</t>
@@ -528,7 +519,7 @@
     <t xml:space="preserve">PA</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocean Test</t>
+    <t xml:space="preserve">Bondex Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Pennsylvania PA usa</t>
@@ -546,7 +537,7 @@
     <t xml:space="preserve">RI</t>
   </si>
   <si>
-    <t xml:space="preserve">Palmetto Test</t>
+    <t xml:space="preserve">United Fire &amp; Casualty Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Rhode Island RI usa</t>
@@ -564,7 +555,7 @@
     <t xml:space="preserve">SC</t>
   </si>
   <si>
-    <t xml:space="preserve">Rushmore Test</t>
+    <t xml:space="preserve">RLI Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">South Carolina SC usa</t>
@@ -582,7 +573,7 @@
     <t xml:space="preserve">TX</t>
   </si>
   <si>
-    <t xml:space="preserve">Beehive Test</t>
+    <t xml:space="preserve">Western Surety Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Texas TX usa</t>
@@ -600,7 +591,7 @@
     <t xml:space="preserve">UT</t>
   </si>
   <si>
-    <t xml:space="preserve">Virginia Test</t>
+    <t xml:space="preserve">Allegheny Casualty Company</t>
   </si>
   <si>
     <t xml:space="preserve">meridian Utah UT USA</t>
@@ -618,10 +609,10 @@
     <t xml:space="preserve">VA</t>
   </si>
   <si>
-    <t xml:space="preserve">Maple Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virginia Avenue  VA USA</t>
+    <t xml:space="preserve">Lexon Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Virginia street VA USA</t>
   </si>
   <si>
     <t xml:space="preserve">41</t>
@@ -636,7 +627,7 @@
     <t xml:space="preserve">VT</t>
   </si>
   <si>
-    <t xml:space="preserve">Evergreen Test</t>
+    <t xml:space="preserve">GRAY CASUALTY &amp; SURETY COMPANY (THE)</t>
   </si>
   <si>
     <t xml:space="preserve">123 Vermont VT usa</t>
@@ -654,7 +645,7 @@
     <t xml:space="preserve">WA</t>
   </si>
   <si>
-    <t xml:space="preserve">Badger Test</t>
+    <t xml:space="preserve">Cincinnati Insurance Company (The)</t>
   </si>
   <si>
     <t xml:space="preserve">123 Washington WA usa</t>
@@ -672,7 +663,7 @@
     <t xml:space="preserve">WI</t>
   </si>
   <si>
-    <t xml:space="preserve">Mountain Test</t>
+    <t xml:space="preserve">Westchester Fire Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Wisconsin WI usa</t>
@@ -690,7 +681,7 @@
     <t xml:space="preserve">CA</t>
   </si>
   <si>
-    <t xml:space="preserve">Landy Test</t>
+    <t xml:space="preserve">Everest National Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 California CA usa</t>
@@ -699,7 +690,7 @@
     <t xml:space="preserve">FL</t>
   </si>
   <si>
-    <t xml:space="preserve">Application</t>
+    <t xml:space="preserve">FCCI Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Florida FL usa</t>
@@ -708,7 +699,7 @@
     <t xml:space="preserve">WV</t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop</t>
+    <t xml:space="preserve">AMERICAN CONTRACTORS INDEMNITY COMPANY</t>
   </si>
   <si>
     <t xml:space="preserve">123  westverginia wv usa</t>
@@ -717,7 +708,7 @@
     <t xml:space="preserve">NJ</t>
   </si>
   <si>
-    <t xml:space="preserve">Window</t>
+    <t xml:space="preserve">Munich Reinsurance America, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">123 New Jersey NJ usa</t>
@@ -1015,7 +1006,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1042,6 +1033,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1313,11 +1308,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="49.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.12"/>
@@ -1410,21 +1405,21 @@
       <c r="D2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="I2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L2" s="6"/>
@@ -1446,7 +1441,7 @@
       <c r="T2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1463,21 +1458,21 @@
       <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="I3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="6"/>
@@ -1499,7 +1494,7 @@
       <c r="T3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1516,21 +1511,21 @@
       <c r="D4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="I4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L4" s="6"/>
@@ -1552,7 +1547,7 @@
       <c r="T4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="U4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1569,21 +1564,21 @@
       <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="I5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="6"/>
@@ -1605,7 +1600,7 @@
       <c r="T5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="U5" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1619,24 +1614,24 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
-      <c r="I6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="8" t="s">
+      <c r="I6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L6" s="6"/>
@@ -1658,7 +1653,7 @@
       <c r="T6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U6" s="9" t="s">
+      <c r="U6" s="10" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1672,24 +1667,24 @@
       <c r="C7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="D7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="I7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L7" s="6"/>
@@ -1711,7 +1706,7 @@
       <c r="T7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U7" s="9" t="s">
+      <c r="U7" s="10" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1725,24 +1720,24 @@
       <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="I8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L8" s="6"/>
@@ -1764,7 +1759,7 @@
       <c r="T8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="U8" s="10" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1778,24 +1773,24 @@
       <c r="C9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="I9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="6"/>
@@ -1817,7 +1812,7 @@
       <c r="T9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U9" s="9" t="s">
+      <c r="U9" s="10" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1831,24 +1826,24 @@
       <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="I10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L10" s="6"/>
@@ -1870,7 +1865,7 @@
       <c r="T10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="U10" s="10" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1884,24 +1879,24 @@
       <c r="C11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="I11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L11" s="6"/>
@@ -1923,7 +1918,7 @@
       <c r="T11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U11" s="9" t="s">
+      <c r="U11" s="10" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1937,24 +1932,24 @@
       <c r="C12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="I12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>90</v>
       </c>
       <c r="L12" s="6"/>
@@ -1976,7 +1971,7 @@
       <c r="T12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U12" s="9" t="s">
+      <c r="U12" s="10" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1990,24 +1985,24 @@
       <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="8" t="s">
+      <c r="I13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L13" s="6"/>
@@ -2029,7 +2024,7 @@
       <c r="T13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U13" s="9" t="s">
+      <c r="U13" s="10" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2043,24 +2038,24 @@
       <c r="C14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L14" s="6"/>
@@ -2082,7 +2077,7 @@
       <c r="T14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U14" s="9" t="s">
+      <c r="U14" s="10" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2096,24 +2091,24 @@
       <c r="C15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
-      <c r="I15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="I15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L15" s="6"/>
@@ -2135,7 +2130,7 @@
       <c r="T15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U15" s="9" t="s">
+      <c r="U15" s="10" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2149,24 +2144,24 @@
       <c r="C16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
-      <c r="I16" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="8" t="s">
+      <c r="I16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L16" s="6"/>
@@ -2188,7 +2183,7 @@
       <c r="T16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U16" s="9" t="s">
+      <c r="U16" s="10" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2202,24 +2197,24 @@
       <c r="C17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="7" t="n">
+      <c r="D17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="8" t="s">
+      <c r="I17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L17" s="6"/>
@@ -2227,13 +2222,13 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="R17" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>31</v>
@@ -2241,13 +2236,13 @@
       <c r="T17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U17" s="9" t="s">
-        <v>124</v>
+      <c r="U17" s="10" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>22</v>
@@ -2255,24 +2250,24 @@
       <c r="C18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="D18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
-      <c r="I18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="8" t="s">
+      <c r="I18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L18" s="6"/>
@@ -2280,13 +2275,13 @@
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="R18" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>31</v>
@@ -2294,13 +2289,13 @@
       <c r="T18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U18" s="9" t="s">
-        <v>130</v>
+      <c r="U18" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>22</v>
@@ -2308,24 +2303,24 @@
       <c r="C19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="7" t="n">
+      <c r="D19" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
-      <c r="I19" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="8" t="s">
+      <c r="I19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L19" s="6"/>
@@ -2333,13 +2328,13 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>31</v>
@@ -2347,13 +2342,13 @@
       <c r="T19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U19" s="9" t="s">
-        <v>136</v>
+      <c r="U19" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>22</v>
@@ -2361,24 +2356,24 @@
       <c r="C20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="F20" s="7" t="n">
+      <c r="D20" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="8" t="s">
+      <c r="I20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L20" s="6"/>
@@ -2386,13 +2381,13 @@
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>31</v>
@@ -2400,13 +2395,13 @@
       <c r="T20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U20" s="9" t="s">
-        <v>142</v>
+      <c r="U20" s="10" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>22</v>
@@ -2414,24 +2409,24 @@
       <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" s="7" t="n">
+      <c r="D21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
-      <c r="I21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="8" t="s">
+      <c r="I21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L21" s="6"/>
@@ -2439,13 +2434,13 @@
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>31</v>
@@ -2453,13 +2448,13 @@
       <c r="T21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U21" s="9" t="s">
-        <v>148</v>
+      <c r="U21" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>22</v>
@@ -2467,24 +2462,24 @@
       <c r="C22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F22" s="7" t="n">
+      <c r="D22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="I22" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="8" t="s">
+      <c r="I22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L22" s="6"/>
@@ -2492,13 +2487,13 @@
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
       <c r="P22" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>31</v>
@@ -2506,13 +2501,13 @@
       <c r="T22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U22" s="9" t="s">
-        <v>154</v>
+      <c r="U22" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>22</v>
@@ -2520,24 +2515,24 @@
       <c r="C23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="F23" s="7" t="n">
+      <c r="D23" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="8" t="s">
+      <c r="I23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L23" s="6"/>
@@ -2545,13 +2540,13 @@
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>31</v>
@@ -2559,13 +2554,13 @@
       <c r="T23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U23" s="9" t="s">
-        <v>160</v>
+      <c r="U23" s="10" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>22</v>
@@ -2573,24 +2568,24 @@
       <c r="C24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F24" s="7" t="n">
+      <c r="D24" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K24" s="8" t="s">
+      <c r="I24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L24" s="6"/>
@@ -2598,13 +2593,13 @@
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
       <c r="P24" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>31</v>
@@ -2612,13 +2607,13 @@
       <c r="T24" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U24" s="9" t="s">
-        <v>166</v>
+      <c r="U24" s="10" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>22</v>
@@ -2626,24 +2621,24 @@
       <c r="C25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="F25" s="7" t="n">
+      <c r="D25" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="8" t="s">
+      <c r="I25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L25" s="6"/>
@@ -2651,13 +2646,13 @@
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
       <c r="P25" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>31</v>
@@ -2665,13 +2660,13 @@
       <c r="T25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U25" s="9" t="s">
-        <v>172</v>
+      <c r="U25" s="10" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>22</v>
@@ -2679,24 +2674,24 @@
       <c r="C26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="D26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="I26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="8" t="s">
+      <c r="I26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L26" s="6"/>
@@ -2704,13 +2699,13 @@
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
       <c r="P26" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>31</v>
@@ -2718,13 +2713,13 @@
       <c r="T26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U26" s="9" t="s">
-        <v>178</v>
+      <c r="U26" s="10" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>22</v>
@@ -2732,24 +2727,24 @@
       <c r="C27" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F27" s="7" t="n">
+      <c r="D27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
-      <c r="I27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" s="8" t="s">
+      <c r="I27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L27" s="6"/>
@@ -2757,13 +2752,13 @@
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
       <c r="P27" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>31</v>
@@ -2771,13 +2766,13 @@
       <c r="T27" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U27" s="9" t="s">
-        <v>184</v>
+      <c r="U27" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>22</v>
@@ -2785,24 +2780,24 @@
       <c r="C28" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="F28" s="7" t="n">
+      <c r="D28" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
-      <c r="I28" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K28" s="8" t="s">
+      <c r="I28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L28" s="6"/>
@@ -2810,13 +2805,13 @@
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
       <c r="P28" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>31</v>
@@ -2824,13 +2819,13 @@
       <c r="T28" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U28" s="9" t="s">
-        <v>190</v>
+      <c r="U28" s="10" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>22</v>
@@ -2838,24 +2833,24 @@
       <c r="C29" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F29" s="7" t="n">
+      <c r="D29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" s="8" t="s">
+      <c r="I29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L29" s="6"/>
@@ -2863,13 +2858,13 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
       <c r="P29" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>31</v>
@@ -2877,13 +2872,13 @@
       <c r="T29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U29" s="9" t="s">
-        <v>196</v>
+      <c r="U29" s="10" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>22</v>
@@ -2891,24 +2886,24 @@
       <c r="C30" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F30" s="7" t="n">
+      <c r="D30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
-      <c r="I30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K30" s="8" t="s">
+      <c r="I30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L30" s="6"/>
@@ -2916,13 +2911,13 @@
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
       <c r="P30" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>31</v>
@@ -2930,13 +2925,13 @@
       <c r="T30" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U30" s="9" t="s">
-        <v>202</v>
+      <c r="U30" s="10" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>22</v>
@@ -2944,24 +2939,24 @@
       <c r="C31" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F31" s="7" t="n">
+      <c r="D31" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="F31" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K31" s="8" t="s">
+      <c r="I31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L31" s="6"/>
@@ -2969,13 +2964,13 @@
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
       <c r="P31" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>31</v>
@@ -2983,13 +2978,13 @@
       <c r="T31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U31" s="9" t="s">
-        <v>208</v>
+      <c r="U31" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>22</v>
@@ -2997,24 +2992,24 @@
       <c r="C32" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F32" s="7" t="n">
+      <c r="D32" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K32" s="8" t="s">
+      <c r="I32" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L32" s="6"/>
@@ -3022,13 +3017,13 @@
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>31</v>
@@ -3036,13 +3031,13 @@
       <c r="T32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U32" s="9" t="s">
-        <v>214</v>
+      <c r="U32" s="10" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>22</v>
@@ -3050,24 +3045,24 @@
       <c r="C33" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="7" t="n">
+      <c r="D33" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
-      <c r="I33" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K33" s="8" t="s">
+      <c r="I33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L33" s="6"/>
@@ -3075,13 +3070,13 @@
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
       <c r="P33" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>31</v>
@@ -3089,13 +3084,13 @@
       <c r="T33" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U33" s="9" t="s">
-        <v>220</v>
+      <c r="U33" s="10" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>22</v>
@@ -3106,29 +3101,29 @@
       <c r="D34" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F34" s="7" t="n">
+      <c r="E34" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K34" s="8" t="s">
+      <c r="I34" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
-      <c r="P34" s="10" t="s">
-        <v>223</v>
+      <c r="P34" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>92</v>
@@ -3142,13 +3137,13 @@
       <c r="T34" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U34" s="9" t="s">
+      <c r="U34" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
-        <v>224</v>
+      <c r="A35" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>22</v>
@@ -3159,29 +3154,29 @@
       <c r="D35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="F35" s="7" t="n">
+      <c r="E35" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
-      <c r="I35" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K35" s="8" t="s">
+      <c r="I35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
-      <c r="P35" s="10" t="s">
-        <v>226</v>
+      <c r="P35" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>98</v>
@@ -3195,13 +3190,13 @@
       <c r="T35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U35" s="9" t="s">
+      <c r="U35" s="10" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
-        <v>227</v>
+      <c r="A36" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>22</v>
@@ -3212,21 +3207,21 @@
       <c r="D36" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F36" s="7" t="n">
+      <c r="E36" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
-      <c r="I36" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K36" s="8" t="s">
+      <c r="I36" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L36" s="6"/>
@@ -3234,7 +3229,7 @@
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>104</v>
@@ -3248,13 +3243,13 @@
       <c r="T36" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U36" s="9" t="s">
+      <c r="U36" s="10" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
-        <v>230</v>
+      <c r="A37" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>22</v>
@@ -3265,21 +3260,21 @@
       <c r="D37" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F37" s="7" t="n">
+      <c r="E37" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
-      <c r="I37" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="8" t="s">
+      <c r="I37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L37" s="6"/>
@@ -3287,7 +3282,7 @@
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>110</v>
@@ -3301,9 +3296,42 @@
       <c r="T37" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U37" s="9" t="s">
+      <c r="U37" s="10" t="s">
         <v>112</v>
       </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E48" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3414,7 +3442,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
@@ -3426,20 +3454,20 @@
         <v>24</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="F2" s="7" t="n">
+        <v>231</v>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="I2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L2" s="6"/>
@@ -3447,7 +3475,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>29</v>
@@ -3461,7 +3489,7 @@
       <c r="T2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3486,7 +3514,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>22</v>
@@ -3494,24 +3522,24 @@
       <c r="C1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F1" s="7" t="n">
+      <c r="D1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F1" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
-      <c r="I1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="I1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L1" s="6"/>
@@ -3519,7 +3547,7 @@
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q1" s="6" t="n">
         <v>6</v>
@@ -3533,13 +3561,13 @@
       <c r="T1" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>220</v>
+      <c r="U1" s="10" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
@@ -3547,24 +3575,24 @@
       <c r="C2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="D2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="I2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L2" s="6"/>
@@ -3572,13 +3600,13 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="S2" s="6" t="s">
         <v>31</v>
@@ -3586,13 +3614,13 @@
       <c r="T2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="9" t="s">
-        <v>244</v>
+      <c r="U2" s="10" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
@@ -3600,24 +3628,24 @@
       <c r="C3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="D3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F3" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="I3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="6"/>
@@ -3625,13 +3653,13 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S3" s="6" t="s">
         <v>31</v>
@@ -3639,13 +3667,13 @@
       <c r="T3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="9" t="s">
-        <v>250</v>
+      <c r="U3" s="10" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>251</v>
+      <c r="A4" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
@@ -3653,24 +3681,24 @@
       <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="D4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="I4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L4" s="6"/>
@@ -3678,13 +3706,13 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S4" s="6" t="s">
         <v>31</v>
@@ -3692,13 +3720,13 @@
       <c r="T4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="9" t="s">
-        <v>250</v>
+      <c r="U4" s="10" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>22</v>
@@ -3706,24 +3734,24 @@
       <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="D5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="I5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="6"/>
@@ -3731,13 +3759,13 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="S5" s="6" t="s">
         <v>31</v>
@@ -3745,13 +3773,13 @@
       <c r="T5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U5" s="9" t="s">
-        <v>257</v>
+      <c r="U5" s="10" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
@@ -3759,24 +3787,24 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="D6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
-      <c r="I6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="8" t="s">
+      <c r="I6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L6" s="6"/>
@@ -3784,13 +3812,13 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="S6" s="6" t="s">
         <v>31</v>
@@ -3798,13 +3826,13 @@
       <c r="T6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U6" s="9" t="s">
-        <v>263</v>
+      <c r="U6" s="10" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
@@ -3812,24 +3840,24 @@
       <c r="C7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="D7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="I7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L7" s="6"/>
@@ -3837,13 +3865,13 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>31</v>
@@ -3851,13 +3879,13 @@
       <c r="T7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U7" s="9" t="s">
-        <v>269</v>
+      <c r="U7" s="10" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>22</v>
@@ -3865,24 +3893,24 @@
       <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="I8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L8" s="6"/>
@@ -3890,13 +3918,13 @@
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="S8" s="6" t="s">
         <v>31</v>
@@ -3904,13 +3932,13 @@
       <c r="T8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U8" s="9" t="s">
-        <v>275</v>
+      <c r="U8" s="10" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>22</v>
@@ -3918,24 +3946,24 @@
       <c r="C9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="D9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="I9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="6"/>
@@ -3943,13 +3971,13 @@
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="S9" s="6" t="s">
         <v>31</v>
@@ -3957,13 +3985,13 @@
       <c r="T9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U9" s="9" t="s">
-        <v>281</v>
+      <c r="U9" s="10" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>22</v>
@@ -3971,24 +3999,24 @@
       <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F10" s="7" t="n">
+      <c r="D10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>46038</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="I10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>27</v>
       </c>
       <c r="L10" s="6"/>
@@ -3996,13 +4024,13 @@
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="S10" s="6" t="s">
         <v>31</v>
@@ -4010,8 +4038,8 @@
       <c r="T10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U10" s="9" t="s">
-        <v>287</v>
+      <c r="U10" s="10" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
